--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488012_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488012_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4605</v>
+        <v>8.430199999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8562</v>
+        <v>4.2472</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6042</v>
+        <v>4.183</v>
       </c>
       <c r="G2" t="n">
         <v>9.784000000000001</v>
@@ -610,13 +610,13 @@
         <v>2.5769</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5486</v>
+        <v>0.5184</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.068</v>
+        <v>-0.6771</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6166</v>
+        <v>1.1955</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2775</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.4363</v>
+        <v>7.711</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0133</v>
+        <v>1.8949</v>
       </c>
       <c r="F3" t="n">
-        <v>5.4231</v>
+        <v>5.8162</v>
       </c>
       <c r="G3" t="n">
         <v>5.6051</v>
@@ -688,13 +688,13 @@
         <v>2.1805</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1593</v>
+        <v>0.434</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2641</v>
+        <v>-0.3825</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4234</v>
+        <v>0.8165</v>
       </c>
       <c r="V3" t="n">
         <v>1.4737</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.1909</v>
+        <v>7.5538</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9287</v>
+        <v>2.3196</v>
       </c>
       <c r="F4" t="n">
-        <v>5.2622</v>
+        <v>5.2342</v>
       </c>
       <c r="G4" t="n">
         <v>4.4125</v>
@@ -766,13 +766,13 @@
         <v>2.7751</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6685</v>
+        <v>-0.3057</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1304</v>
+        <v>-0.7395</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4618</v>
+        <v>0.4338</v>
       </c>
       <c r="V4" t="n">
         <v>0.8701</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6172</v>
+        <v>1.2899</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2354</v>
+        <v>0.7677</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3818</v>
+        <v>0.5222</v>
       </c>
       <c r="G5" t="n">
         <v>1.401</v>
@@ -844,13 +844,13 @@
         <v>0.9911</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-0.1111</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8736</v>
+        <v>-0.3413</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0898</v>
+        <v>0.2302</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. SENZI KITAMBO</t>
+          <t>J. MARTINEZ GUZMAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2948</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.8188</v>
+        <v>-0.7663</v>
       </c>
       <c r="F8" t="n">
-        <v>4.1136</v>
+        <v>0.1277</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1713</v>
+        <v>-0.7391</v>
       </c>
       <c r="H8" t="n">
-        <v>2.534</v>
+        <v>0.2003</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.3627</v>
+        <v>-0.9394</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5535</v>
+        <v>-0.6186</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.0605</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.5156</v>
+        <v>-0.6791</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7247</v>
+        <v>-0.1205</v>
       </c>
       <c r="N8" t="n">
-        <v>1.5718</v>
+        <v>0.1398</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1529</v>
+        <v>-0.2602</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3876</v>
+        <v>0.9911</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1716</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.784</v>
+        <v>0.9911</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4517</v>
+        <v>-0.6241</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9766</v>
+        <v>-0.1477</v>
       </c>
       <c r="U8" t="n">
-        <v>1.475</v>
+        <v>-0.4763</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9405</v>
+        <v>-0.2666</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0704</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8701</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. URBANO MORENO</t>
+          <t>S. OKUNGHAE FRANCIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2376</v>
+        <v>-0.6878</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3167</v>
+        <v>-0.5226</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0791</v>
+        <v>-0.1653</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0756</v>
+        <v>-0.9668</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0748</v>
+        <v>-0.5153</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1504</v>
+        <v>-0.4515</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4232</v>
+        <v>-0.5786</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9351</v>
+        <v>0.0202</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3583</v>
+        <v>-0.5988</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6524</v>
+        <v>-0.3882</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1398</v>
+        <v>-0.5355</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7922</v>
+        <v>0.1472</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9911</v>
+        <v>0.1982</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0451</v>
+        <v>0.0808</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3047</v>
+        <v>0.056</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2596</v>
+        <v>0.0247</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MARTINEZ GUZMAN</t>
+          <t>R. URBANO MORENO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8247</v>
+        <v>-0.8416</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8682</v>
+        <v>-0.7241</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0435</v>
+        <v>-0.1175</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7391</v>
+        <v>-1.0756</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2003</v>
+        <v>1.0748</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9394</v>
+        <v>-2.1504</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6186</v>
+        <v>-0.4232</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0605</v>
+        <v>0.9351</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6791</v>
+        <v>-1.3583</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1205</v>
+        <v>-0.6524</v>
       </c>
       <c r="N10" t="n">
         <v>0.1398</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2602</v>
+        <v>-0.7922</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9911</v>
+        <v>0.7929</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R10" t="n">
         <v>0.9911</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8102</v>
+        <v>-0.5589</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2496</v>
+        <v>-0.1027</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5606</v>
+        <v>-0.4562</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. OKUNGHAE FRANCIS</t>
+          <t>E. SENZI KITAMBO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1962</v>
+        <v>-1.2906</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8905999999999999</v>
+        <v>-4.8146</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3057</v>
+        <v>3.524</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9668</v>
+        <v>0.1713</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5153</v>
+        <v>2.534</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4515</v>
+        <v>-2.3627</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5786</v>
+        <v>-1.5535</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0202</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5988</v>
+        <v>-2.5156</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3882</v>
+        <v>1.7247</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5355</v>
+        <v>1.5718</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1472</v>
+        <v>0.1529</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1982</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.1716</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1982</v>
+        <v>1.784</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4276</v>
+        <v>0.8662</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.312</v>
+        <v>-0.0191</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1157</v>
+        <v>0.8854</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.9405</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.0704</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5385</v>
+        <v>-2.2505</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3844</v>
+        <v>-1.1806</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1541</v>
+        <v>-1.0699</v>
       </c>
       <c r="G12" t="n">
         <v>-1.795</v>
@@ -1390,13 +1390,13 @@
         <v>0.5947</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.131</v>
+        <v>0.1569</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1872</v>
+        <v>0.0165</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0562</v>
+        <v>0.1404</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2071</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.4568</v>
+        <v>-4.5938</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.8852</v>
+        <v>-7.4153</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4284</v>
+        <v>2.8215</v>
       </c>
       <c r="G13" t="n">
         <v>-3.153</v>
@@ -1468,13 +1468,13 @@
         <v>2.7751</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.9074</v>
+        <v>-1.0444</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4351</v>
+        <v>-0.9653</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4722</v>
+        <v>-0.0791</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.6539</v>
+        <v>15.59</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.222300000000001</v>
+        <v>-5.286100000000001</v>
       </c>
       <c r="F14" t="n">
         <v>20.8761</v>
@@ -1528,7 +1528,7 @@
         <v>1.1302</v>
       </c>
       <c r="M14" t="n">
-        <v>6.457999999999999</v>
+        <v>6.457999999999998</v>
       </c>
       <c r="N14" t="n">
         <v>5.550800000000001</v>
@@ -1546,13 +1546,13 @@
         <v>15.8578</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5238</v>
+        <v>-0.5879000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.2387</v>
+        <v>-3.3027</v>
       </c>
       <c r="U14" t="n">
-        <v>2.714700000000001</v>
+        <v>2.7149</v>
       </c>
       <c r="V14" t="n">
         <v>-1.3479</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1488</v>
+        <v>1.8878</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2323</v>
+        <v>1.1117</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9165</v>
+        <v>0.7761</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1358</v>
@@ -1624,13 +1624,13 @@
         <v>2.1805</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6721</v>
+        <v>0.4112</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1052</v>
+        <v>-0.0153</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5669</v>
+        <v>0.4265</v>
       </c>
       <c r="V15" t="n">
         <v>2.4142</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5239</v>
+        <v>1.4612</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2334</v>
+        <v>-0.6222</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7573</v>
+        <v>2.0834</v>
       </c>
       <c r="G16" t="n">
         <v>0.999</v>
@@ -1702,13 +1702,13 @@
         <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1196</v>
+        <v>0.0569</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.5489</v>
+        <v>-0.9377</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6685</v>
+        <v>0.9946</v>
       </c>
       <c r="V16" t="n">
         <v>0.6036</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6415</v>
+        <v>0.603</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-0.6728</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4162</v>
+        <v>1.2758</v>
       </c>
       <c r="G17" t="n">
         <v>1.0127</v>
@@ -1780,13 +1780,13 @@
         <v>1.784</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0936</v>
+        <v>0.0551</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.444</v>
+        <v>-0.3422</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5376</v>
+        <v>0.3972</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2666</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1923</v>
+        <v>0.3503</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6939</v>
+        <v>0.7957</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5016</v>
+        <v>-0.4454</v>
       </c>
       <c r="G18" t="n">
         <v>0.3421</v>
@@ -1858,13 +1858,13 @@
         <v>0.1982</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.348</v>
+        <v>-0.1899</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.312</v>
+        <v>-0.2101</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.036</v>
+        <v>0.0202</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1954</v>
+        <v>-0.3566</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9607</v>
+        <v>-1.757</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7654</v>
+        <v>1.4004</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7733</v>
@@ -1936,13 +1936,13 @@
         <v>1.3876</v>
       </c>
       <c r="S19" t="n">
-        <v>0.12</v>
+        <v>-0.0413</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8184</v>
+        <v>-0.6147</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9384</v>
+        <v>0.5734</v>
       </c>
       <c r="V19" t="n">
         <v>0.0704</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7147</v>
+        <v>-1.4058</v>
       </c>
       <c r="E20" t="n">
         <v>-1.9262</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2115</v>
+        <v>0.5203</v>
       </c>
       <c r="G20" t="n">
         <v>-3.1196</v>
@@ -2014,13 +2014,13 @@
         <v>0.7929</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0619</v>
+        <v>0.2469</v>
       </c>
       <c r="T20" t="n">
         <v>0.0038</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.06569999999999999</v>
+        <v>0.2431</v>
       </c>
       <c r="V20" t="n">
         <v>0.674</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4883</v>
+        <v>-1.7262</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9831</v>
+        <v>-2.4737</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4948</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>-0.436</v>
@@ -2092,13 +2092,13 @@
         <v>0.9911</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0612</v>
+        <v>-0.2991</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6753</v>
+        <v>-0.166</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3859</v>
+        <v>-0.1332</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0913</v>
+        <v>-3.3303</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7507</v>
+        <v>-3.1582</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3406</v>
+        <v>-0.1721</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7287</v>
@@ -2170,13 +2170,13 @@
         <v>1.3876</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8356</v>
+        <v>0.5966</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3085</v>
+        <v>-0.0989</v>
       </c>
       <c r="U22" t="n">
-        <v>0.527</v>
+        <v>0.6955</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6036</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9498</v>
+        <v>-3.957</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1819</v>
+        <v>-4.3856</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2321</v>
+        <v>0.4286</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8643</v>
@@ -2248,13 +2248,13 @@
         <v>1.5858</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5092</v>
+        <v>0.502</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5471</v>
+        <v>0.3434</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0379</v>
+        <v>0.1587</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2071</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1706</v>
+        <v>-3.9917</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6912</v>
+        <v>-3.793</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4794</v>
+        <v>-0.1986</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1583</v>
@@ -2326,13 +2326,13 @@
         <v>0.3964</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.08069999999999999</v>
+        <v>0.0982</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2568</v>
+        <v>-0.3587</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1762</v>
+        <v>0.4569</v>
       </c>
       <c r="V24" t="n">
         <v>-0.337</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5504</v>
+        <v>-4.1886</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.3006</v>
+        <v>-3.995</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2498</v>
+        <v>-0.1937</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6901</v>
@@ -2404,13 +2404,13 @@
         <v>0.3964</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2745</v>
+        <v>0.0872</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.624</v>
+        <v>-0.3184</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3494</v>
+        <v>0.4056</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-14.654</v>
+        <v>-14.6539</v>
       </c>
       <c r="E26" t="n">
         <v>-20.8763</v>
       </c>
       <c r="F26" t="n">
-        <v>6.2224</v>
+        <v>6.222300000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-14.5523</v>
